--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>32641</x:v>
+        <x:v>37141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2431</x:v>
+        <x:v>2461</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>246182</x:v>
+        <x:v>250712</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>9481</x:v>
+        <x:v>9661</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2461</x:v>
+        <x:v>2491</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>250712</x:v>
+        <x:v>250922</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>59904</x:v>
+        <x:v>59954</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>9661</x:v>
+        <x:v>10021</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2491</x:v>
+        <x:v>2581</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>250922</x:v>
+        <x:v>251422</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>59954</x:v>
+        <x:v>59904</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10021</x:v>
+        <x:v>9661</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2581</x:v>
+        <x:v>2521</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>251422</x:v>
+        <x:v>250952</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>8641</x:v>
+        <x:v>9001</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2521</x:v>
+        <x:v>2551</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>250952</x:v>
+        <x:v>251342</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>9661</x:v>
+        <x:v>9841</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2551</x:v>
+        <x:v>2581</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>251342</x:v>
+        <x:v>251552</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>9841</x:v>
+        <x:v>10021</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2581</x:v>
+        <x:v>2611</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>251552</x:v>
+        <x:v>251762</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10021</x:v>
+        <x:v>10201</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2611</x:v>
+        <x:v>2641</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>251762</x:v>
+        <x:v>251972</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10201</x:v>
+        <x:v>10381</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2641</x:v>
+        <x:v>2671</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>251972</x:v>
+        <x:v>252182</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10381</x:v>
+        <x:v>10561</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2671</x:v>
+        <x:v>2701</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>252182</x:v>
+        <x:v>252392</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10561</x:v>
+        <x:v>10741</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2701</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>252392</x:v>
+        <x:v>252602</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10741</x:v>
+        <x:v>10921</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2731</x:v>
+        <x:v>2761</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>252602</x:v>
+        <x:v>252812</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>10921</x:v>
+        <x:v>12001</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2761</x:v>
+        <x:v>2941</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>252812</x:v>
+        <x:v>254072</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>12001</x:v>
+        <x:v>12361</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2941</x:v>
+        <x:v>3001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254072</x:v>
+        <x:v>254492</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>59904</x:v>
+        <x:v>59304</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>2380</x:v>
+        <x:v>1780</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>12361</x:v>
+        <x:v>12721</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3001</x:v>
+        <x:v>3061</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254492</x:v>
+        <x:v>253712</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>12721</x:v>
+        <x:v>12901</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3061</x:v>
+        <x:v>3091</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>253712</x:v>
+        <x:v>253922</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>12901</x:v>
+        <x:v>13081</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3091</x:v>
+        <x:v>3121</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>253922</x:v>
+        <x:v>254132</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>13081</x:v>
+        <x:v>13441</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3121</x:v>
+        <x:v>3181</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254132</x:v>
+        <x:v>254552</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>13441</x:v>
+        <x:v>14161</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3181</x:v>
+        <x:v>3301</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254552</x:v>
+        <x:v>255392</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>14161</x:v>
+        <x:v>15061</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3301</x:v>
+        <x:v>3451</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>255392</x:v>
+        <x:v>256442</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>15061</x:v>
+        <x:v>15241</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3451</x:v>
+        <x:v>3481</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>256442</x:v>
+        <x:v>256652</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>15241</x:v>
+        <x:v>15601</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3481</x:v>
+        <x:v>3541</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>256652</x:v>
+        <x:v>257072</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>59304</x:v>
+        <x:v>59400</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>59440</x:v>
+        <x:v>59620</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>59440</x:v>
+        <x:v>59620</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>15601</x:v>
+        <x:v>15961</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3541</x:v>
+        <x:v>3631</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>257072</x:v>
+        <x:v>257978</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>15961</x:v>
+        <x:v>16501</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3631</x:v>
+        <x:v>3721</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>257978</x:v>
+        <x:v>258608</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>16501</x:v>
+        <x:v>17221</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3721</x:v>
+        <x:v>3841</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>258608</x:v>
+        <x:v>259448</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>17221</x:v>
+        <x:v>18121</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3841</x:v>
+        <x:v>3991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>259448</x:v>
+        <x:v>260498</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>18121</x:v>
+        <x:v>18301</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3991</x:v>
+        <x:v>4021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>260498</x:v>
+        <x:v>260708</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>18301</x:v>
+        <x:v>18661</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4021</x:v>
+        <x:v>4081</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>260708</x:v>
+        <x:v>261128</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>18661</x:v>
+        <x:v>18721</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4081</x:v>
+        <x:v>4111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>261128</x:v>
+        <x:v>261218</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>59620</x:v>
+        <x:v>64120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>37141</x:v>
+        <x:v>50641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>59620</x:v>
+        <x:v>64120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>18721</x:v>
+        <x:v>19441</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4111</x:v>
+        <x:v>4501</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>261218</x:v>
+        <x:v>284828</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>19441</x:v>
+        <x:v>19801</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4501</x:v>
+        <x:v>4561</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>284828</x:v>
+        <x:v>285248</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>19801</x:v>
+        <x:v>19981</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4561</x:v>
+        <x:v>4591</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>285248</x:v>
+        <x:v>285458</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>64120</x:v>
+        <x:v>64620</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>50641</x:v>
+        <x:v>52141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>64120</x:v>
+        <x:v>64620</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>19981</x:v>
+        <x:v>21061</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4591</x:v>
+        <x:v>4831</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>285458</x:v>
+        <x:v>289278</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>21061</x:v>
+        <x:v>22321</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4831</x:v>
+        <x:v>5041</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>289278</x:v>
+        <x:v>290748</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>22321</x:v>
+        <x:v>22501</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5041</x:v>
+        <x:v>5071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>290748</x:v>
+        <x:v>290958</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>22501</x:v>
+        <x:v>22861</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5071</x:v>
+        <x:v>5131</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>290958</x:v>
+        <x:v>291378</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>22861</x:v>
+        <x:v>23041</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5131</x:v>
+        <x:v>5161</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>291378</x:v>
+        <x:v>291588</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23041</x:v>
+        <x:v>23401</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5161</x:v>
+        <x:v>5221</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>291588</x:v>
+        <x:v>292008</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23401</x:v>
+        <x:v>23761</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5221</x:v>
+        <x:v>5281</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>292008</x:v>
+        <x:v>292428</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23761</x:v>
+        <x:v>25201</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5281</x:v>
+        <x:v>5521</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>292428</x:v>
+        <x:v>294108</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>25201</x:v>
+        <x:v>25381</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5521</x:v>
+        <x:v>5551</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>294108</x:v>
+        <x:v>294318</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>25381</x:v>
+        <x:v>26281</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5551</x:v>
+        <x:v>5701</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>294318</x:v>
+        <x:v>295368</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>26281</x:v>
+        <x:v>27721</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5701</x:v>
+        <x:v>5941</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>295368</x:v>
+        <x:v>297048</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>27721</x:v>
+        <x:v>28801</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5941</x:v>
+        <x:v>6121</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>297048</x:v>
+        <x:v>298308</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>28801</x:v>
+        <x:v>29701</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6121</x:v>
+        <x:v>6271</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>298308</x:v>
+        <x:v>299358</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>59400</x:v>
+        <x:v>60840</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>64620</x:v>
+        <x:v>67320</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>9001</x:v>
+        <x:v>11761</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>52141</x:v>
+        <x:v>53101</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>64620</x:v>
+        <x:v>67320</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>29701</x:v>
+        <x:v>32881</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6271</x:v>
+        <x:v>6961</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>299358</x:v>
+        <x:v>313788</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>32881</x:v>
+        <x:v>33061</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6961</x:v>
+        <x:v>6991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>313788</x:v>
+        <x:v>313998</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>33061</x:v>
+        <x:v>33241</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6991</x:v>
+        <x:v>7051</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>313998</x:v>
+        <x:v>314238</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>33241</x:v>
+        <x:v>33601</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7051</x:v>
+        <x:v>7111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>314238</x:v>
+        <x:v>314658</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>33601</x:v>
+        <x:v>35221</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7111</x:v>
+        <x:v>7381</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>314658</x:v>
+        <x:v>316548</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>35221</x:v>
+        <x:v>35401</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7381</x:v>
+        <x:v>7411</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>316548</x:v>
+        <x:v>316758</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>35401</x:v>
+        <x:v>35761</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7411</x:v>
+        <x:v>7471</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>316758</x:v>
+        <x:v>317178</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>60840</x:v>
+        <x:v>60890</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>53101</x:v>
+        <x:v>54541</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>5320</x:v>
+        <x:v>6520</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7471</x:v>
+        <x:v>7531</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>317178</x:v>
+        <x:v>320408</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>35761</x:v>
+        <x:v>36121</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7531</x:v>
+        <x:v>7591</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>320408</x:v>
+        <x:v>320828</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>36121</x:v>
+        <x:v>36321</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7591</x:v>
+        <x:v>7621</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>320828</x:v>
+        <x:v>321058</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>67320</x:v>
+        <x:v>67820</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>54541</x:v>
+        <x:v>59041</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>67320</x:v>
+        <x:v>67820</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>36321</x:v>
+        <x:v>36501</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7621</x:v>
+        <x:v>7711</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>321058</x:v>
+        <x:v>326828</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>36501</x:v>
+        <x:v>36681</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>326828</x:v>
+        <x:v>327008</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>36681</x:v>
+        <x:v>36861</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>327008</x:v>
+        <x:v>327188</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>36861</x:v>
+        <x:v>37221</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7711</x:v>
+        <x:v>7712</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>327188</x:v>
+        <x:v>327549</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>37221</x:v>
+        <x:v>38121</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7712</x:v>
+        <x:v>7802</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>327549</x:v>
+        <x:v>328539</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>60890</x:v>
+        <x:v>61130</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>67820</x:v>
+        <x:v>68180</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>67820</x:v>
+        <x:v>68180</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7802</x:v>
+        <x:v>7832</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>328539</x:v>
+        <x:v>329529</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>38121</x:v>
+        <x:v>38301</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7832</x:v>
+        <x:v>7882</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>329529</x:v>
+        <x:v>329759</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>38301</x:v>
+        <x:v>38481</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>329759</x:v>
+        <x:v>329939</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>38481</x:v>
+        <x:v>38661</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>329939</x:v>
+        <x:v>330119</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>38661</x:v>
+        <x:v>39201</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>330119</x:v>
+        <x:v>330659</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>39201</x:v>
+        <x:v>39381</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>330659</x:v>
+        <x:v>330839</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>6520</x:v>
+        <x:v>6760</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>39381</x:v>
+        <x:v>40161</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7882</x:v>
+        <x:v>7912</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>330839</x:v>
+        <x:v>331889</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>40161</x:v>
+        <x:v>40521</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>331889</x:v>
+        <x:v>332249</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>1</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>332249</x:v>
+        <x:v>332499</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>40521</x:v>
+        <x:v>40881</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>251</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>332499</x:v>
+        <x:v>332909</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIV.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIV.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>40881</x:v>
+        <x:v>41061</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>332909</x:v>
+        <x:v>333089</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
